--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2023_magallanes.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2023_magallanes.xlsx
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="C2">
-        <v>1996</v>
+        <v>2018</v>
       </c>
       <c r="D2">
-        <v>1973</v>
+        <v>2121</v>
       </c>
       <c r="E2">
-        <v>101.1657374556513</v>
+        <v>95.14380009429514</v>
       </c>
     </row>
     <row r="3">

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2023_magallanes.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2023_magallanes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t xml:space="preserve">Categoria</t>
   </si>
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 21:13</t>
+    <t xml:space="preserve">2026-08-07 07:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -60,16 +60,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_regional_cobertura_2023_magallanes.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Cobertura de residentes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Region de Magallanes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023</t>
   </si>
   <si>
     <t xml:space="preserve">region</t>
@@ -609,23 +618,23 @@
         <v>14</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -648,10 +657,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -665,10 +674,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>91119</v>
@@ -682,10 +691,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>93326</v>
@@ -718,10 +727,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -735,10 +744,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>2018</v>
@@ -752,10 +761,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>8210</v>
@@ -769,10 +778,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>29456</v>
@@ -786,10 +795,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>144761</v>
@@ -822,10 +831,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -839,10 +848,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>7653</v>
@@ -856,10 +865,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>10188</v>
@@ -873,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>11469</v>
@@ -890,10 +899,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>11331</v>
@@ -907,10 +916,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>11268</v>
@@ -924,10 +933,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>13959</v>
@@ -941,10 +950,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>16101</v>
@@ -958,10 +967,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>15616</v>
@@ -975,10 +984,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>13748</v>
@@ -992,10 +1001,10 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>12591</v>
@@ -1009,10 +1018,10 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>11136</v>
@@ -1026,10 +1035,10 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>11242</v>
@@ -1043,10 +1052,10 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>11016</v>
@@ -1060,10 +1069,10 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>9510</v>
@@ -1077,10 +1086,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>6578</v>
@@ -1094,10 +1103,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>4740</v>
@@ -1111,10 +1120,10 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>6299</v>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2023_magallanes.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2023_magallanes.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-07 07:12</t>
+    <t xml:space="preserve">2026-08-28 11:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Tierra del Fuego</t>
   </si>
   <si>
-    <t xml:space="preserve">Ultima Esperanza</t>
+    <t xml:space="preserve">Última Esperanza</t>
   </si>
   <si>
     <t xml:space="preserve">Tramo_Edad</t>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2023_magallanes.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2023_magallanes.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:12</t>
+    <t xml:space="preserve">2026-09-01 13:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2023_magallanes.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2023_magallanes.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01 13:20</t>
+    <t xml:space="preserve">2026-09-06 17:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2023_magallanes.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2023_magallanes.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:17</t>
+    <t xml:space="preserve">2026-09-08 13:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
